--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/38.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/38.xlsx
@@ -426,13 +426,13 @@
         <v>-7.555506582368153</v>
       </c>
       <c r="E2">
-        <v>-11.58418728082697</v>
+        <v>-8.977950862984507</v>
       </c>
       <c r="F2">
-        <v>-2.147972561687279</v>
+        <v>-2.601121837347318</v>
       </c>
       <c r="G2">
-        <v>-5.707946293795755</v>
+        <v>-4.525781227915894</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.198757844162241</v>
       </c>
       <c r="E3">
-        <v>-12.43443544661112</v>
+        <v>-9.062425017123591</v>
       </c>
       <c r="F3">
-        <v>-2.203722516263089</v>
+        <v>-2.701326128594363</v>
       </c>
       <c r="G3">
-        <v>-6.344667337406002</v>
+        <v>-3.806803241031927</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.823807045032853</v>
       </c>
       <c r="E4">
-        <v>-12.81652544100831</v>
+        <v>-11.03161382546302</v>
       </c>
       <c r="F4">
-        <v>-1.887918212722013</v>
+        <v>-1.956978374726005</v>
       </c>
       <c r="G4">
-        <v>-6.553359591029804</v>
+        <v>-3.701548215848059</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.319309164267342</v>
       </c>
       <c r="E5">
-        <v>-12.82357627503825</v>
+        <v>-11.08389958635558</v>
       </c>
       <c r="F5">
-        <v>-1.824427993134445</v>
+        <v>-2.160073352707374</v>
       </c>
       <c r="G5">
-        <v>-5.863269478755189</v>
+        <v>-3.880338697400642</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.696374552371145</v>
       </c>
       <c r="E6">
-        <v>-13.93490455278663</v>
+        <v>-11.062896523908</v>
       </c>
       <c r="F6">
-        <v>-1.807278302794287</v>
+        <v>-2.514797670301581</v>
       </c>
       <c r="G6">
-        <v>-6.129281391800932</v>
+        <v>-4.847295003639643</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.950310363783998</v>
       </c>
       <c r="E7">
-        <v>-14.7506231042623</v>
+        <v>-13.27281448202117</v>
       </c>
       <c r="F7">
-        <v>-1.839986389693826</v>
+        <v>-1.881620963725932</v>
       </c>
       <c r="G7">
-        <v>-5.43650724029069</v>
+        <v>-3.933261519932926</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.08569552776468</v>
       </c>
       <c r="E8">
-        <v>-15.05740457591192</v>
+        <v>-14.23850703568287</v>
       </c>
       <c r="F8">
-        <v>-1.588342454969183</v>
+        <v>-1.695185282582264</v>
       </c>
       <c r="G8">
-        <v>-5.808499328484938</v>
+        <v>-4.422658996745665</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.11113800454976</v>
       </c>
       <c r="E9">
-        <v>-15.63867044258848</v>
+        <v>-14.53639005590743</v>
       </c>
       <c r="F9">
-        <v>-1.770167443148869</v>
+        <v>-1.843438196661291</v>
       </c>
       <c r="G9">
-        <v>-5.07546458844031</v>
+        <v>-3.538307443265685</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.04132464561815</v>
       </c>
       <c r="E10">
-        <v>-16.19690901893602</v>
+        <v>-15.06059262161332</v>
       </c>
       <c r="F10">
-        <v>-1.710194471553588</v>
+        <v>-2.010737762432888</v>
       </c>
       <c r="G10">
-        <v>-4.78497804378267</v>
+        <v>-3.685050233847171</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.88634916155034</v>
       </c>
       <c r="E11">
-        <v>-16.25703809680987</v>
+        <v>-16.29363722373986</v>
       </c>
       <c r="F11">
-        <v>-1.508415769375268</v>
+        <v>-1.352483061104886</v>
       </c>
       <c r="G11">
-        <v>-4.290458580115637</v>
+        <v>-3.816722373806128</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.675589497836132</v>
       </c>
       <c r="E12">
-        <v>-17.95141193151981</v>
+        <v>-16.23011179036026</v>
       </c>
       <c r="F12">
-        <v>-1.426048713412704</v>
+        <v>-1.75176277619347</v>
       </c>
       <c r="G12">
-        <v>-2.735166123381961</v>
+        <v>-2.743424958047084</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.42649661489075</v>
       </c>
       <c r="E13">
-        <v>-17.66985858856691</v>
+        <v>-16.93751830052047</v>
       </c>
       <c r="F13">
-        <v>-1.31333110417897</v>
+        <v>-1.552775672162584</v>
       </c>
       <c r="G13">
-        <v>-2.860105196700938</v>
+        <v>-1.542593022715541</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.166003681400303</v>
       </c>
       <c r="E14">
-        <v>-19.6653578308909</v>
+        <v>-16.384636908924</v>
       </c>
       <c r="F14">
-        <v>-1.426545733854384</v>
+        <v>-1.067640645978248</v>
       </c>
       <c r="G14">
-        <v>-2.268064547065649</v>
+        <v>-1.91694102798947</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.909706979358949</v>
       </c>
       <c r="E15">
-        <v>-19.22406709579144</v>
+        <v>-18.78053023758418</v>
       </c>
       <c r="F15">
-        <v>-0.972368454247471</v>
+        <v>-1.259806972814483</v>
       </c>
       <c r="G15">
-        <v>-2.259172436639554</v>
+        <v>-0.6450279900156771</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.654116109603619</v>
       </c>
       <c r="E16">
-        <v>-20.81386035176824</v>
+        <v>-18.84963927941524</v>
       </c>
       <c r="F16">
-        <v>-0.5731135901809709</v>
+        <v>-1.310179166211318</v>
       </c>
       <c r="G16">
-        <v>-1.976705197473196</v>
+        <v>0.1647479598612437</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.394709200099983</v>
       </c>
       <c r="E17">
-        <v>-21.09994669720282</v>
+        <v>-18.62063434884735</v>
       </c>
       <c r="F17">
-        <v>-0.8400317914458332</v>
+        <v>-0.4796977697998678</v>
       </c>
       <c r="G17">
-        <v>-1.31888589923572</v>
+        <v>-0.1162066361662101</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.107119070904876</v>
       </c>
       <c r="E18">
-        <v>-21.48091815852011</v>
+        <v>-21.16320042214196</v>
       </c>
       <c r="F18">
-        <v>-0.3921865522659197</v>
+        <v>-0.2519099879084486</v>
       </c>
       <c r="G18">
-        <v>-1.592487277748458</v>
+        <v>0.09113047295354208</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.771095837969283</v>
       </c>
       <c r="E19">
-        <v>-23.21606184472111</v>
+        <v>-20.05346163877028</v>
       </c>
       <c r="F19">
-        <v>-0.2005263579127953</v>
+        <v>-0.2149059876579919</v>
       </c>
       <c r="G19">
-        <v>-0.0652623902342714</v>
+        <v>0.815489663194998</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.376688158808477</v>
       </c>
       <c r="E20">
-        <v>-23.66530910865205</v>
+        <v>-21.64989816611633</v>
       </c>
       <c r="F20">
-        <v>0.3842372441736401</v>
+        <v>0.03755720242801903</v>
       </c>
       <c r="G20">
-        <v>-1.167959551165941</v>
+        <v>0.3408544021782011</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.918477229186395</v>
       </c>
       <c r="E21">
-        <v>-23.12058349874339</v>
+        <v>-20.75720008498427</v>
       </c>
       <c r="F21">
-        <v>0.3342767493759963</v>
+        <v>0.3042840508228347</v>
       </c>
       <c r="G21">
-        <v>-0.5549650206520386</v>
+        <v>1.153091268224705</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.415974125487115</v>
       </c>
       <c r="E22">
-        <v>-24.01445445464343</v>
+        <v>-21.4952598357024</v>
       </c>
       <c r="F22">
-        <v>0.6289262061843777</v>
+        <v>0.3403793320324203</v>
       </c>
       <c r="G22">
-        <v>-1.130117222920865</v>
+        <v>0.9899390886244358</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.889627154384317</v>
       </c>
       <c r="E23">
-        <v>-24.94136968537745</v>
+        <v>-22.80766141633936</v>
       </c>
       <c r="F23">
-        <v>0.6786713254572936</v>
+        <v>0.8431411881809271</v>
       </c>
       <c r="G23">
-        <v>-0.7852706806879037</v>
+        <v>0.7862572603219051</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.365159808355881</v>
       </c>
       <c r="E24">
-        <v>-24.91081607124769</v>
+        <v>-22.96698218887721</v>
       </c>
       <c r="F24">
-        <v>0.8977935559480272</v>
+        <v>1.105105752377048</v>
       </c>
       <c r="G24">
-        <v>-1.449905076104347</v>
+        <v>1.517100144364824</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.877512407887319</v>
       </c>
       <c r="E25">
-        <v>-25.60504019357158</v>
+        <v>-22.7559688855418</v>
       </c>
       <c r="F25">
-        <v>1.200808695157281</v>
+        <v>0.5916546432628167</v>
       </c>
       <c r="G25">
-        <v>-1.613172098459197</v>
+        <v>1.312427387151341</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.448343616045452</v>
       </c>
       <c r="E26">
-        <v>-24.85735290711314</v>
+        <v>-23.24944122663165</v>
       </c>
       <c r="F26">
-        <v>1.284283278337387</v>
+        <v>1.172090854037028</v>
       </c>
       <c r="G26">
-        <v>-1.126793345481147</v>
+        <v>1.063753448825704</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.104536404795841</v>
       </c>
       <c r="E27">
-        <v>-25.04805147605014</v>
+        <v>-22.72570056527453</v>
       </c>
       <c r="F27">
-        <v>1.49973335613151</v>
+        <v>1.082594039838569</v>
       </c>
       <c r="G27">
-        <v>-1.572094485756509</v>
+        <v>0.8710374629748376</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.861218606684552</v>
       </c>
       <c r="E28">
-        <v>-24.57213602868804</v>
+        <v>-21.52160649747903</v>
       </c>
       <c r="F28">
-        <v>1.289806832179254</v>
+        <v>1.686478846683825</v>
       </c>
       <c r="G28">
-        <v>-2.119950205872315</v>
+        <v>0.4098420854655262</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.721607141546496</v>
       </c>
       <c r="E29">
-        <v>-24.35784411017107</v>
+        <v>-22.4265903285939</v>
       </c>
       <c r="F29">
-        <v>1.422938727687579</v>
+        <v>0.8563354241727176</v>
       </c>
       <c r="G29">
-        <v>-2.030907696413663</v>
+        <v>-0.09408135919087433</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.68922937761145</v>
       </c>
       <c r="E30">
-        <v>-23.66681256202259</v>
+        <v>-22.35635369673493</v>
       </c>
       <c r="F30">
-        <v>1.398155631730624</v>
+        <v>0.8061595538503459</v>
       </c>
       <c r="G30">
-        <v>-2.148404959235819</v>
+        <v>-1.206595935028402</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.748513841289711</v>
       </c>
       <c r="E31">
-        <v>-24.17465375113878</v>
+        <v>-21.63906152781598</v>
       </c>
       <c r="F31">
-        <v>1.63479866115797</v>
+        <v>1.293691875298384</v>
       </c>
       <c r="G31">
-        <v>-2.064651778930993</v>
+        <v>-0.3124433727503607</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.881384740857254</v>
       </c>
       <c r="E32">
-        <v>-23.90140562951595</v>
+        <v>-21.19100978102306</v>
       </c>
       <c r="F32">
-        <v>1.179198246353047</v>
+        <v>1.714126437119662</v>
       </c>
       <c r="G32">
-        <v>-2.35190960157414</v>
+        <v>-0.8757569276327106</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.066451421301418</v>
       </c>
       <c r="E33">
-        <v>-24.07352386959948</v>
+        <v>-21.1206010671518</v>
       </c>
       <c r="F33">
-        <v>1.342875361472202</v>
+        <v>1.070779863939842</v>
       </c>
       <c r="G33">
-        <v>-2.521670161395131</v>
+        <v>-1.144915532153961</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.273931586851587</v>
       </c>
       <c r="E34">
-        <v>-22.19145837269363</v>
+        <v>-19.67485404088499</v>
       </c>
       <c r="F34">
-        <v>1.479546042525286</v>
+        <v>1.60560533714851</v>
       </c>
       <c r="G34">
-        <v>-2.302996431787498</v>
+        <v>-0.7108132010609842</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.484170560488827</v>
       </c>
       <c r="E35">
-        <v>-22.54483331340818</v>
+        <v>-20.40314134469457</v>
       </c>
       <c r="F35">
-        <v>1.293327393641152</v>
+        <v>0.7521748502099022</v>
       </c>
       <c r="G35">
-        <v>-2.602004308835016</v>
+        <v>-0.3863889818140068</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.676655852459364</v>
       </c>
       <c r="E36">
-        <v>-22.07770763409496</v>
+        <v>-20.68780574929073</v>
       </c>
       <c r="F36">
-        <v>1.371763846277432</v>
+        <v>0.9429246687873499</v>
       </c>
       <c r="G36">
-        <v>-2.169211185144258</v>
+        <v>-0.2780660144720584</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.835269149146926</v>
       </c>
       <c r="E37">
-        <v>-22.43428873440694</v>
+        <v>-21.4506815375709</v>
       </c>
       <c r="F37">
-        <v>1.230116333868327</v>
+        <v>0.7525310481931059</v>
       </c>
       <c r="G37">
-        <v>-2.115979927785387</v>
+        <v>-0.1987424832724824</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.954967586657713</v>
       </c>
       <c r="E38">
-        <v>-21.3764145638451</v>
+        <v>-18.91809169251518</v>
       </c>
       <c r="F38">
-        <v>1.517902766744515</v>
+        <v>0.8171138843849666</v>
       </c>
       <c r="G38">
-        <v>-2.372551766404607</v>
+        <v>-0.8673143445602594</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.028488660113242</v>
       </c>
       <c r="E39">
-        <v>-20.78015039125515</v>
+        <v>-17.85123302952213</v>
       </c>
       <c r="F39">
-        <v>1.229713747310567</v>
+        <v>1.118053134882805</v>
       </c>
       <c r="G39">
-        <v>-2.067933000490437</v>
+        <v>0.01075695085494377</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.059702853846363</v>
       </c>
       <c r="E40">
-        <v>-20.45589353840992</v>
+        <v>-17.66027633756669</v>
       </c>
       <c r="F40">
-        <v>1.373708852939205</v>
+        <v>1.292248859282707</v>
       </c>
       <c r="G40">
-        <v>-1.417522700534187</v>
+        <v>-0.9873840850850198</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.054973581595454</v>
       </c>
       <c r="E41">
-        <v>-19.66370946635211</v>
+        <v>-16.67128931360953</v>
       </c>
       <c r="F41">
-        <v>0.9615877863724227</v>
+        <v>1.056255269899156</v>
       </c>
       <c r="G41">
-        <v>-1.615075206963675</v>
+        <v>-1.173386691625262</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.020009118384629</v>
       </c>
       <c r="E42">
-        <v>-19.35319653212016</v>
+        <v>-15.89324313740367</v>
       </c>
       <c r="F42">
-        <v>1.201376955195601</v>
+        <v>1.637018685797472</v>
       </c>
       <c r="G42">
-        <v>-1.503595704481541</v>
+        <v>-0.9066561910580015</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.967265237700578</v>
       </c>
       <c r="E43">
-        <v>-18.26920212348208</v>
+        <v>-16.82211919738301</v>
       </c>
       <c r="F43">
-        <v>1.084073504019969</v>
+        <v>1.267813677634927</v>
       </c>
       <c r="G43">
-        <v>-1.070038056167432</v>
+        <v>-0.4713102769939955</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.901627641554493</v>
       </c>
       <c r="E44">
-        <v>-18.77042268359906</v>
+        <v>-14.99808156641144</v>
       </c>
       <c r="F44">
-        <v>0.8593871296846309</v>
+        <v>1.091454257578912</v>
       </c>
       <c r="G44">
-        <v>-1.276400642484029</v>
+        <v>-0.5967645020978047</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.82923736278388</v>
       </c>
       <c r="E45">
-        <v>-18.15762052393309</v>
+        <v>-15.91454055066175</v>
       </c>
       <c r="F45">
-        <v>0.9066686843016212</v>
+        <v>0.6786406758633901</v>
       </c>
       <c r="G45">
-        <v>-1.578965363701986</v>
+        <v>-1.049107143839734</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.755186018209189</v>
       </c>
       <c r="E46">
-        <v>-16.84974741730381</v>
+        <v>-16.000296262945</v>
       </c>
       <c r="F46">
-        <v>1.351120930599668</v>
+        <v>0.7367904108051098</v>
       </c>
       <c r="G46">
-        <v>-0.7689925405314985</v>
+        <v>0.5595511003367508</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.678143444307358</v>
       </c>
       <c r="E47">
-        <v>-16.88195392444636</v>
+        <v>-15.15121191498081</v>
       </c>
       <c r="F47">
-        <v>0.9908540067133292</v>
+        <v>0.597326474869785</v>
       </c>
       <c r="G47">
-        <v>-1.068741973651452</v>
+        <v>0.7252593515318279</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.602015737340841</v>
       </c>
       <c r="E48">
-        <v>-16.552308187532</v>
+        <v>-14.18901987172705</v>
       </c>
       <c r="F48">
-        <v>0.8127102832716844</v>
+        <v>1.391326570861945</v>
       </c>
       <c r="G48">
-        <v>-0.9923781042984947</v>
+        <v>-0.4281195576070247</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.524153164157473</v>
       </c>
       <c r="E49">
-        <v>-15.43585367720694</v>
+        <v>-13.96318940143854</v>
       </c>
       <c r="F49">
-        <v>1.261827894782298</v>
+        <v>0.4450029633734007</v>
       </c>
       <c r="G49">
-        <v>-0.7925320239989548</v>
+        <v>0.8125168764621412</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.441159938132597</v>
       </c>
       <c r="E50">
-        <v>-15.23718046554243</v>
+        <v>-13.66193719655227</v>
       </c>
       <c r="F50">
-        <v>0.9558886186411621</v>
+        <v>0.5168936567927586</v>
       </c>
       <c r="G50">
-        <v>-0.8814596907030255</v>
+        <v>-0.6721505674260472</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.353735840656923</v>
       </c>
       <c r="E51">
-        <v>-15.12812575448971</v>
+        <v>-12.54584043567382</v>
       </c>
       <c r="F51">
-        <v>1.027525831635263</v>
+        <v>0.6193693314582798</v>
       </c>
       <c r="G51">
-        <v>-0.3527761481590552</v>
+        <v>-0.6300820258124065</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.256420085189385</v>
       </c>
       <c r="E52">
-        <v>-14.86654298191064</v>
+        <v>-12.35750573016882</v>
       </c>
       <c r="F52">
-        <v>1.111896708345199</v>
+        <v>-0.08433540415912262</v>
       </c>
       <c r="G52">
-        <v>-0.5674205376916907</v>
+        <v>0.18645652169853</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.15251575500056</v>
       </c>
       <c r="E53">
-        <v>-12.83156903166179</v>
+        <v>-12.74906023524204</v>
       </c>
       <c r="F53">
-        <v>0.9793049083834986</v>
+        <v>0.2043191577551987</v>
       </c>
       <c r="G53">
-        <v>-1.381298014517917</v>
+        <v>0.05043676317330872</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.044623011396762</v>
       </c>
       <c r="E54">
-        <v>-13.19770521212995</v>
+        <v>-10.55721994536748</v>
       </c>
       <c r="F54">
-        <v>0.6827245271591916</v>
+        <v>0.8468406770018296</v>
       </c>
       <c r="G54">
-        <v>-1.213430719536726</v>
+        <v>0.3909717802771597</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.935176939252905</v>
       </c>
       <c r="E55">
-        <v>-12.37053414988889</v>
+        <v>-12.32590603854329</v>
       </c>
       <c r="F55">
-        <v>1.151633492657491</v>
+        <v>0.3917952683567828</v>
       </c>
       <c r="G55">
-        <v>-1.017709134737408</v>
+        <v>-0.1195239511628087</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.833452352907359</v>
       </c>
       <c r="E56">
-        <v>-12.43507848992021</v>
+        <v>-8.551164830131615</v>
       </c>
       <c r="F56">
-        <v>0.7290932208982968</v>
+        <v>0.3115703704978591</v>
       </c>
       <c r="G56">
-        <v>-1.26570386020024</v>
+        <v>-0.5153081768845897</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.741771452975244</v>
       </c>
       <c r="E57">
-        <v>-11.72698818018484</v>
+        <v>-9.44159414578583</v>
       </c>
       <c r="F57">
-        <v>0.9514286885444896</v>
+        <v>0.7676504100290025</v>
       </c>
       <c r="G57">
-        <v>-2.107189535227634</v>
+        <v>-0.6232964596274747</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.667385697566167</v>
       </c>
       <c r="E58">
-        <v>-11.18785523567566</v>
+        <v>-9.985907664559791</v>
       </c>
       <c r="F58">
-        <v>0.7525211077842723</v>
+        <v>0.763409168926669</v>
       </c>
       <c r="G58">
-        <v>-1.999542499526931</v>
+        <v>-0.5530619121475606</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.616299731006762</v>
       </c>
       <c r="E59">
-        <v>-10.90336744156579</v>
+        <v>-9.239384195921325</v>
       </c>
       <c r="F59">
-        <v>1.110831427865199</v>
+        <v>0.9390959546516106</v>
       </c>
       <c r="G59">
-        <v>-2.09114436180195</v>
+        <v>-0.1194616079531792</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.588802046957978</v>
       </c>
       <c r="E60">
-        <v>-10.34963922532988</v>
+        <v>-9.367472083228281</v>
       </c>
       <c r="F60">
-        <v>1.089578833778974</v>
+        <v>1.062231112342952</v>
       </c>
       <c r="G60">
-        <v>-2.469249365761442</v>
+        <v>-0.984493328891149</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.590662126387194</v>
       </c>
       <c r="E61">
-        <v>-10.10076335081633</v>
+        <v>-9.320525393190762</v>
       </c>
       <c r="F61">
-        <v>1.120775150168404</v>
+        <v>0.3317154373665403</v>
       </c>
       <c r="G61">
-        <v>-2.6483089074819</v>
+        <v>-1.55104873067423</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.621035474800803</v>
       </c>
       <c r="E62">
-        <v>-10.03477895605057</v>
+        <v>-9.599542790699363</v>
       </c>
       <c r="F62">
-        <v>0.9901084760508098</v>
+        <v>1.493252209572007</v>
       </c>
       <c r="G62">
-        <v>-2.550315225609084</v>
+        <v>-1.941779875194467</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.678403421049883</v>
       </c>
       <c r="E63">
-        <v>-9.555358469806524</v>
+        <v>-8.929609402952627</v>
       </c>
       <c r="F63">
-        <v>0.8272928630305669</v>
+        <v>0.3800349363392382</v>
       </c>
       <c r="G63">
-        <v>-2.821938027521476</v>
+        <v>-2.316282097881689</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.764666163044275</v>
       </c>
       <c r="E64">
-        <v>-9.94318604077143</v>
+        <v>-8.183221788534391</v>
       </c>
       <c r="F64">
-        <v>0.6893266153595037</v>
+        <v>0.424277210955357</v>
       </c>
       <c r="G64">
-        <v>-3.389983103892546</v>
+        <v>-2.225982880565771</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.873170209902085</v>
       </c>
       <c r="E65">
-        <v>-9.35995028790154</v>
+        <v>-7.619281863411185</v>
       </c>
       <c r="F65">
-        <v>0.8618954261803079</v>
+        <v>0.4689344976402784</v>
       </c>
       <c r="G65">
-        <v>-3.008094851475013</v>
+        <v>-3.225587341321246</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.003586015704304</v>
       </c>
       <c r="E66">
-        <v>-10.31888635834379</v>
+        <v>-7.406570382322894</v>
       </c>
       <c r="F66">
-        <v>0.7311840202229627</v>
+        <v>0.3337184297465095</v>
       </c>
       <c r="G66">
-        <v>-3.102564501392986</v>
+        <v>-2.84833217374565</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.153523773409556</v>
       </c>
       <c r="E67">
-        <v>-9.336112400725163</v>
+        <v>-9.37316890352993</v>
       </c>
       <c r="F67">
-        <v>0.4497089185887047</v>
+        <v>0.003054043366614025</v>
       </c>
       <c r="G67">
-        <v>-3.0891246178855</v>
+        <v>-2.727586501579644</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.317966582887282</v>
       </c>
       <c r="E68">
-        <v>-9.939916482537891</v>
+        <v>-8.540065540338814</v>
       </c>
       <c r="F68">
-        <v>0.6899876525469376</v>
+        <v>0.3366110887170853</v>
       </c>
       <c r="G68">
-        <v>-3.257431596555658</v>
+        <v>-2.240515410852551</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.499873350765764</v>
       </c>
       <c r="E69">
-        <v>-8.918487470789788</v>
+        <v>-7.280841829973934</v>
       </c>
       <c r="F69">
-        <v>0.4799617245063454</v>
+        <v>0.03918245927231166</v>
       </c>
       <c r="G69">
-        <v>-3.442512179837696</v>
+        <v>-2.3793242077033</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.69351629078769</v>
       </c>
       <c r="E70">
-        <v>-9.636155503051379</v>
+        <v>-7.921457876995013</v>
       </c>
       <c r="F70">
-        <v>0.2648984942893294</v>
+        <v>-0.1471480192112007</v>
       </c>
       <c r="G70">
-        <v>-3.349269706782956</v>
+        <v>-3.448779313016236</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.89770758429133</v>
       </c>
       <c r="E71">
-        <v>-8.74394649711215</v>
+        <v>-8.862769126599412</v>
       </c>
       <c r="F71">
-        <v>0.2134129751031317</v>
+        <v>-0.01974097082362277</v>
       </c>
       <c r="G71">
-        <v>-3.237389895270569</v>
+        <v>-2.25612090058927</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.111344172273411</v>
       </c>
       <c r="E72">
-        <v>-9.117989393197705</v>
+        <v>-8.536311435386455</v>
       </c>
       <c r="F72">
-        <v>0.1199308853298047</v>
+        <v>-0.5164010726831083</v>
       </c>
       <c r="G72">
-        <v>-2.943084008717735</v>
+        <v>-2.601781185768974</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.326693542833683</v>
       </c>
       <c r="E73">
-        <v>-9.829910791943563</v>
+        <v>-8.846507376437868</v>
       </c>
       <c r="F73">
-        <v>0.1491341497480984</v>
+        <v>-0.1086736668207749</v>
       </c>
       <c r="G73">
-        <v>-3.441862497968926</v>
+        <v>-3.409007626494206</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.543621259905758</v>
       </c>
       <c r="E74">
-        <v>-10.32062529236274</v>
+        <v>-8.348927709423064</v>
       </c>
       <c r="F74">
-        <v>0.230657099327209</v>
+        <v>0.1921537540776852</v>
       </c>
       <c r="G74">
-        <v>-3.25641113665067</v>
+        <v>-2.438871816564103</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.755413907532376</v>
       </c>
       <c r="E75">
-        <v>-10.71060841695529</v>
+        <v>-9.23486477886167</v>
       </c>
       <c r="F75">
-        <v>0.09533417203847895</v>
+        <v>0.3298507823428386</v>
       </c>
       <c r="G75">
-        <v>-3.275494721240401</v>
+        <v>-1.24259421675707</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.956138215066562</v>
       </c>
       <c r="E76">
-        <v>-11.32594199359155</v>
+        <v>-10.01722659079684</v>
       </c>
       <c r="F76">
-        <v>0.105894199689367</v>
+        <v>-0.4537599296834097</v>
       </c>
       <c r="G76">
-        <v>-2.871999624853924</v>
+        <v>-1.045839047166528</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.14496150346264</v>
       </c>
       <c r="E77">
-        <v>-10.58632897628879</v>
+        <v>-9.785889496114999</v>
       </c>
       <c r="F77">
-        <v>-0.4174285637640262</v>
+        <v>-0.9713263680547493</v>
       </c>
       <c r="G77">
-        <v>-2.948150214805517</v>
+        <v>-2.425648493679541</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.313363732331288</v>
       </c>
       <c r="E78">
-        <v>-11.73070152887113</v>
+        <v>-10.91645473144796</v>
       </c>
       <c r="F78">
-        <v>-0.1390772356057252</v>
+        <v>0.1712639849138872</v>
       </c>
       <c r="G78">
-        <v>-2.323185788042761</v>
+        <v>-3.071675081632373</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.461150328838336</v>
       </c>
       <c r="E79">
-        <v>-11.51332571955494</v>
+        <v>-12.38666910277822</v>
       </c>
       <c r="F79">
-        <v>-0.4534012465979976</v>
+        <v>-0.4582140612082627</v>
       </c>
       <c r="G79">
-        <v>-1.901096009078912</v>
+        <v>-3.260683287121067</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.585299492481457</v>
       </c>
       <c r="E80">
-        <v>-13.15954376166732</v>
+        <v>-12.50955377345036</v>
       </c>
       <c r="F80">
-        <v>-0.344122190453284</v>
+        <v>-0.5550013369187597</v>
       </c>
       <c r="G80">
-        <v>-2.204143069866106</v>
+        <v>-3.110347558931989</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.680731417823616</v>
       </c>
       <c r="E81">
-        <v>-13.29200615486568</v>
+        <v>-12.96148642246784</v>
       </c>
       <c r="F81">
-        <v>-0.5082930125445068</v>
+        <v>-0.9048531974497002</v>
       </c>
       <c r="G81">
-        <v>-2.063175229229243</v>
+        <v>-2.235980762657399</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.750372038838408</v>
       </c>
       <c r="E82">
-        <v>-14.49847767151521</v>
+        <v>-11.52625904132085</v>
       </c>
       <c r="F82">
-        <v>-0.5187685467203094</v>
+        <v>-0.8785285097561346</v>
       </c>
       <c r="G82">
-        <v>-2.11933005499758</v>
+        <v>-0.872085240707692</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.786484290211424</v>
       </c>
       <c r="E83">
-        <v>-15.15801368294034</v>
+        <v>-13.98008060948715</v>
       </c>
       <c r="F83">
-        <v>-0.6615451238994293</v>
+        <v>-1.200367469826604</v>
       </c>
       <c r="G83">
-        <v>-2.181387798351357</v>
+        <v>0.332434787656666</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.787359547712415</v>
       </c>
       <c r="E84">
-        <v>-15.98380356060906</v>
+        <v>-15.40684880118781</v>
       </c>
       <c r="F84">
-        <v>-0.7919516906525443</v>
+        <v>-0.8287800770136076</v>
       </c>
       <c r="G84">
-        <v>-1.525858792762373</v>
+        <v>-1.145798180753451</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.749759774582246</v>
       </c>
       <c r="E85">
-        <v>-16.93355588576376</v>
+        <v>-17.0317603730941</v>
       </c>
       <c r="F85">
-        <v>-0.8250143188004809</v>
+        <v>-1.273064164728886</v>
       </c>
       <c r="G85">
-        <v>-0.5639555677249171</v>
+        <v>0.3544583467636588</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.66834763139872</v>
       </c>
       <c r="E86">
-        <v>-18.29322114961877</v>
+        <v>-17.98745405614686</v>
       </c>
       <c r="F86">
-        <v>-1.213695901337648</v>
+        <v>-1.654016251030531</v>
       </c>
       <c r="G86">
-        <v>-1.025669378240621</v>
+        <v>0.3817121730364066</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.548301735053736</v>
       </c>
       <c r="E87">
-        <v>-19.88702210509236</v>
+        <v>-17.51161106436887</v>
       </c>
       <c r="F87">
-        <v>-1.079585703926617</v>
+        <v>-1.236813150447574</v>
       </c>
       <c r="G87">
-        <v>-0.6610337887826484</v>
+        <v>0.5164883485905983</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.389367395882107</v>
       </c>
       <c r="E88">
-        <v>-21.07076068222338</v>
+        <v>-19.87284345297434</v>
       </c>
       <c r="F88">
-        <v>-1.212971908227601</v>
+        <v>-1.537614891956547</v>
       </c>
       <c r="G88">
-        <v>-0.9509986192123374</v>
+        <v>-0.2733213680971014</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.198989178952611</v>
       </c>
       <c r="E89">
-        <v>-21.97681323320406</v>
+        <v>-20.03701874964842</v>
       </c>
       <c r="F89">
-        <v>-1.433252196347449</v>
+        <v>-1.598019442968687</v>
       </c>
       <c r="G89">
-        <v>-0.115763671255685</v>
+        <v>0.9672986598642673</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.988601422186768</v>
       </c>
       <c r="E90">
-        <v>-23.93960783624465</v>
+        <v>-23.13130239671954</v>
       </c>
       <c r="F90">
-        <v>-1.402138716698299</v>
+        <v>-1.960078953914684</v>
       </c>
       <c r="G90">
-        <v>-0.7007825067537617</v>
+        <v>-0.8535791511124238</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.764641641709806</v>
       </c>
       <c r="E91">
-        <v>-25.82932192574946</v>
+        <v>-25.23095654121995</v>
       </c>
       <c r="F91">
-        <v>-1.735192114667869</v>
+        <v>-1.65764367188739</v>
       </c>
       <c r="G91">
-        <v>0.001658123470603578</v>
+        <v>0.7446809019421812</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.543314871372272</v>
       </c>
       <c r="E92">
-        <v>-28.00592390058821</v>
+        <v>-26.80706927721958</v>
       </c>
       <c r="F92">
-        <v>-1.988709816457643</v>
+        <v>-1.600393543945111</v>
       </c>
       <c r="G92">
-        <v>-0.2059021087151908</v>
+        <v>0.8717166758376428</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.334923914831512</v>
       </c>
       <c r="E93">
-        <v>-30.86775418413459</v>
+        <v>-28.95106171072909</v>
       </c>
       <c r="F93">
-        <v>-2.031938169372736</v>
+        <v>-1.604791346486573</v>
       </c>
       <c r="G93">
-        <v>-0.3517228760384734</v>
+        <v>0.03755796855248821</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.14894621967488</v>
       </c>
       <c r="E94">
-        <v>-31.53072730733154</v>
+        <v>-31.2244711386668</v>
       </c>
       <c r="F94">
-        <v>-2.153404995114838</v>
+        <v>-2.385915299569617</v>
       </c>
       <c r="G94">
-        <v>-0.1456687245484642</v>
+        <v>-0.4968775553851887</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.999251286875907</v>
       </c>
       <c r="E95">
-        <v>-34.59966508538172</v>
+        <v>-32.85199337583851</v>
       </c>
       <c r="F95">
-        <v>-2.512329963808642</v>
+        <v>-2.32970145924824</v>
       </c>
       <c r="G95">
-        <v>-0.5684147478242024</v>
+        <v>0.002685145818709773</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.887978843289518</v>
       </c>
       <c r="E96">
-        <v>-36.52747496247606</v>
+        <v>-35.83809630734039</v>
       </c>
       <c r="F96">
-        <v>-2.297619618105218</v>
+        <v>-2.550912832328834</v>
       </c>
       <c r="G96">
-        <v>-1.464532761816352</v>
+        <v>-0.259159615846538</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.821520229419685</v>
       </c>
       <c r="E97">
-        <v>-38.58878198907951</v>
+        <v>-39.15239812831118</v>
       </c>
       <c r="F97">
-        <v>-2.702802279306151</v>
+        <v>-3.208832044858702</v>
       </c>
       <c r="G97">
-        <v>-0.8646270241030741</v>
+        <v>-0.9161947021313073</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.800133292759422</v>
       </c>
       <c r="E98">
-        <v>-41.53721480954859</v>
+        <v>-38.82993228693598</v>
       </c>
       <c r="F98">
-        <v>-2.730334726672999</v>
+        <v>-2.697255531177006</v>
       </c>
       <c r="G98">
-        <v>-1.217108968904863</v>
+        <v>-0.2596124244217414</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.813365319641586</v>
       </c>
       <c r="E99">
-        <v>-43.83477911784322</v>
+        <v>-41.19252548198075</v>
       </c>
       <c r="F99">
-        <v>-2.745667807298818</v>
+        <v>-3.191032914474749</v>
       </c>
       <c r="G99">
-        <v>-1.366329081763731</v>
+        <v>-1.274471284207076</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.859552409096993</v>
       </c>
       <c r="E100">
-        <v>-45.81472758042487</v>
+        <v>-44.26560228527395</v>
       </c>
       <c r="F100">
-        <v>-2.769857792195368</v>
+        <v>-3.058540518601385</v>
       </c>
       <c r="G100">
-        <v>-1.867463488094603</v>
+        <v>-0.8092432854012068</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.915338491004139</v>
       </c>
       <c r="E101">
-        <v>-48.11186168368877</v>
+        <v>-46.71039634050596</v>
       </c>
       <c r="F101">
-        <v>-3.378680497128713</v>
+        <v>-3.466149467925118</v>
       </c>
       <c r="G101">
-        <v>-2.112098242680563</v>
+        <v>-1.230676820053167</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.973675850600601</v>
       </c>
       <c r="E102">
-        <v>-50.58529494066379</v>
+        <v>-49.86474566681481</v>
       </c>
       <c r="F102">
-        <v>-2.977517902933565</v>
+        <v>-3.957423524931602</v>
       </c>
       <c r="G102">
-        <v>-2.611473914255574</v>
+        <v>-0.8290749885064906</v>
       </c>
     </row>
   </sheetData>
